--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0044.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0044.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Four letters&lt;/color&gt;... cấp độ bảo mật cao nhất trong kho. Liệu có thể là...</t>
+          <t>&lt;color=yellow&gt;Bốn chữ cái&lt;/color&gt;... cấp độ bảo mật cao nhất trong kho. Liệu có thể là...</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Đó là chuyện ta biết, còn ngươi cứ đoán đi.</t>
+          <t>Đó là chuyện tao biết, còn mày cứ đoán đi.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Chỉ có &lt;color=yellow&gt;Grandfather, Uncle, and I&lt;/color&gt; mới có quyền truy cập cao nhất thôi.</t>
+          <t>Chỉ có &lt;color=yellow&gt;ông nội, chú và cháu&lt;/color&gt; mới có quyền truy cập cao nhất thôi.</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Quá trình phục hồi ban đầu gần hoàn tất, nhưng một số dữ liệu đã bị &lt;color=yellow&gt;overwritten&lt;/color&gt; hoặc &lt;color=yellow&gt;isolated&lt;/color&gt; do hư hại quá nặng... Chúng tôi chỉ khôi phục được một số phần nhất định.</t>
+          <t>Quá trình phục hồi ban đầu gần hoàn tất, nhưng một số dữ liệu đã bị &lt;color=yellow&gt;ghi đè&lt;/color&gt; hoặc &lt;color=yellow&gt;cô lập&lt;/color&gt; do hư hại quá nặng... Chúng tôi chỉ khôi phục được một số phần nhất định.</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Đánh giá của chúng tôi cho thấy việc phục hồi hoàn toàn có thể không đáng công. Nhưng nếu anh nhất quyết, &lt;color=yellow&gt;Mr. Pierre&lt;/color&gt; ở trụ sở chính là chuyên gia trong lĩnh vực này.</t>
+          <t>Đánh giá của chúng tôi cho thấy việc phục hồi hoàn toàn có thể không đáng công. Nhưng nếu anh nhất quyết, &lt;color=yellow&gt;ông Pierre&lt;/color&gt; ở trụ sở chính là chuyên gia trong lĩnh vực này.</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Khi cậu và Carlotta xem xét dữ liệu dự đoán, các ngươi nhận ra một mô hình di chuyển giữa Margherita's, nhà Benett và kho tiền, chỉ có hai điểm lệch—&lt;color=yellow&gt;Liberty Square&lt;/color&gt; và &lt;color=yellow&gt;a dock&lt;/color&gt;.</t>
+          <t>Khi cậu và Carlotta xem xét dữ liệu dự đoán, các ngươi nhận ra một mô hình di chuyển giữa Margherita's, nhà Benett và kho tiền, chỉ có hai điểm lệch—&lt;color=yellow&gt;Quảng trường Liberty&lt;/color&gt; và &lt;color=yellow&gt;một bến tàu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Có thể còn &lt;color=yellow&gt;other useful information&lt;/color&gt; trong Thiết bị đầu cuối.</t>
+          <t>Có thể còn &lt;color=yellow&gt;thông tin hữu ích khác&lt;/color&gt; trong Thiết bị đầu cuối.</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Thiết bị đầu cuối của Benett bị hư hại nghiêm trọng, chỉ khôi phục được dữ liệu cơ bản. Dữ liệu thu hồi cho thấy lộ trình di chuyển của Benett, và ngươi phát hiện hai tọa độ khả nghi: một chỉ đến Quảng trường Liberty mà Carlotta từng điều tra, còn cái kia là bến tàu riêng của Capollo.</t>
+          <t>Thiết bị đầu cuối của Benett bị hư hại nghiêm trọng, chỉ khôi phục được dữ liệu cơ bản. Dữ liệu thu hồi cho thấy lộ trình di chuyển của Benett, và mày phát hiện hai tọa độ khả nghi: một chỉ đến Quảng trường Liberty mà Carlotta từng điều tra, còn cái kia là bến tàu riêng của Capollo.</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Thiết bị đầu cuối dạng đèn lồng của chúng ta là một mẫu cải tiến. Trông có vẻ chỉ để trang trí, nhưng bên trong chứa các mô-đun công nghệ mà chúng ta phát triển. Như Scarlet Velvet đã nói, ngoài việc kinh doanh nghệ thuật, chúng ta còn bí mật cung cấp những Thiết bị đầu cuối này cho Cộng Hưởng Giả với giá cả hợp lý.</t>
+          <t>Thiết bị đầu cuối dạng đèn lồng của chúng ta là một mẫu cải tiến. Trông có vẻ chỉ để trang trí, nhưng bên trong chứa các mô-đun công nghệ mà chúng ta phát triển. Như Scarlet Velvet đã nói, ngoài việc kinh doanh nghệ thuật, chúng ta còn bí mật cung cấp những Thiết bị đầu cuối này cho Resonator với giá cả hợp lý.</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Có quan trọng không? Cậu chỉ cần biết là mọi chuyện đã được giải quyết, và ta vô tội rồi.</t>
+          <t>Có quan trọng không? Cậu chỉ cần biết là mọi chuyện đã được giải quyết, và tao vô tội rồi.</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Chúng ta đã đi quá sâu rồi. Giao mô-đun dữ liệu cho Hội sẽ củng cố vị thế của chúng ta như đồng minh của chính quyền. Chúng ta sẽ thay thế Fisalias! Những Cộng Hưởng Giả khác trong thành phố chẳng còn quan trọng nữa.</t>
+          <t>Chúng ta đã đi quá sâu rồi. Giao mô-đun dữ liệu cho Hội sẽ củng cố vị thế của chúng ta như đồng minh của chính quyền. Chúng ta sẽ thay thế Fisalias! Những Resonator khác trong thành phố chẳng còn quan trọng nữa.</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Có thể phiền {Male=anh;Female=chị} cho tôi mượn lửa được không?</t>
+          <t>Có thể phiền {Male=man;Female=lady} cho tôi mượn lửa được không?</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Ta muốn vén màn bí mật về con cá mập đang lẩn khuất này.</t>
+          <t>Tao muốn vén màn bí mật về con cá mập đang lẩn khuất này.</t>
         </is>
       </c>
     </row>
@@ -18926,7 +18926,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Ta sẽ đến nói chuyện với bọn họ xem chúng biết gì.</t>
+          <t>Tao sẽ đến nói chuyện với bọn họ xem chúng biết gì.</t>
         </is>
       </c>
     </row>
@@ -20098,7 +20098,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Capollo &lt;color=yellow&gt;couldn't have tampered&lt;/color&gt; vào dữ liệu Thiết bị đầu cuối, nếu không hắn đã phát hiện ra thông tin bị ẩn dưới các lớp ghi đè. Hắn chỉ đơn giản đặt bẫy tại &lt;color=yellow&gt;the dock that Benett visited&lt;/color&gt;.</t>
+          <t>Capollo &lt;color=yellow&gt;không thể tự mình can thiệp&lt;/color&gt; vào dữ liệu Thiết bị đầu cuối, nếu không hắn đã phát hiện ra thông tin bị ẩn dưới các lớp ghi đè. Hắn chỉ đơn giản đặt bẫy tại &lt;color=yellow&gt;bến tàu mà Benett đã đến&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Như ta đã nói, chúng ta sẽ giành quyền kiểm soát.</t>
+          <t>Như tao đã nói, chúng ta sẽ giành quyền kiểm soát.</t>
         </is>
       </c>
     </row>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Từ khi đến đây, ta chưa gặp thử thách thực sự nào. Cậu có muốn nhận sự giúp đỡ của ta không? Ta chắc chắn sẽ học được đôi điều đấy.</t>
+          <t>Từ khi đến đây, tao chưa gặp thử thách thực sự nào. Cậu có muốn nhận sự giúp đỡ của tao không? Tao chắc chắn sẽ học được đôi điều đấy.</t>
         </is>
       </c>
     </row>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Nhưng có điều ta có thể nói cho ngươi biết. Gần đây có kẻ định trộm đồ trong kho.</t>
+          <t>Nhưng có điều tao có thể nói cho mày biết. Gần đây có kẻ định trộm đồ trong kho.</t>
         </is>
       </c>
     </row>
@@ -22180,7 +22180,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Thật lòng mà nói, ta nghi ngờ là chúng ta sẽ chẳng bao giờ tìm lại được đống đồ đó đâu. Kẻ trộm chắc đã bán sạch từ đời tám hoánh rồi, mà nhân lực của chúng ta thì thiếu trầm trọng. Giống như mò kim đáy bể ấy.</t>
+          <t>Thật lòng mà nói, tao nghi ngờ là chúng ta sẽ chẳng bao giờ tìm lại được đống đồ đó đâu. Kẻ trộm chắc đã bán sạch từ đời tám hoánh rồi, mà nhân lực của chúng ta thì thiếu trầm trọng. Giống như mò kim đáy bể ấy.</t>
         </is>
       </c>
     </row>
@@ -23675,7 +23675,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>(*Một cái thẻ?... Tiếc quá, ta không có.*)</t>
+          <t>(*Một cái thẻ?... Tiếc quá, tao không có.*)</t>
         </is>
       </c>
     </row>
@@ -24000,7 +24000,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Đừng có mà bảo ngươi đã quên ta rồi à?</t>
+          <t>Đừng có mà bảo mày đã quên tao rồi à?</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Điều khiển để vô hiệu hóa camera, rồi đặt những "viên ngọc" ta làm từ Forte của mình vào vị trí.</t>
+          <t>Điều khiển để vô hiệu hóa camera, rồi đặt những "viên ngọc" tao làm từ Forte của mình vào vị trí.</t>
         </is>
       </c>
     </row>
@@ -24585,7 +24585,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Mọi thứ ổn. Ta vừa đến chỗ hẹn rồi.</t>
+          <t>Mọi thứ ổn. Tao vừa đến chỗ hẹn rồi.</t>
         </is>
       </c>
     </row>
@@ -25300,7 +25300,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Ha, Carlotta… Có vẻ như cậu đã ghép được toàn bộ câu chuyện rồi. Vậy ra chính đội của cậu đã báo cho chúng ta về việc đổi thời gian và địa điểm giao dịch hôm qua.</t>
+          <t>Ha, Carlotta… Có vẻ như cậu đã ghép được toàn bộ câu chuyện rồi. Vậy ra chính đội của cậu đã báo cho chúng tao về việc đổi thời gian và địa điểm giao dịch hôm qua.</t>
         </is>
       </c>
     </row>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Lời hứa về sự an toàn và sung túc của Capollo chỉ là trò lừa bịp. Hắn &lt;color=yellow&gt;using our family as pawns&lt;/color&gt;, bắt họ phải trả giá bằng cả mạng sống. Benett chỉ là một trong những nạn nhân của hắn.</t>
+          <t>Lời hứa về sự an toàn và sung túc của Capollo chỉ là trò lừa bịp. Hắn &lt;color=yellow&gt;đã lợi dụng gia tộc ta như những con cờ&lt;/color&gt;, bắt họ phải trả giá bằng cả mạng sống. Benett chỉ là một trong những nạn nhân của hắn.</t>
         </is>
       </c>
     </row>
@@ -25625,7 +25625,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Ta không thể đảm bảo sẽ không có thêm tổn thất, nhưng ta sẽ ưu tiên phúc lợi của từng thành viên. Ta không coi nhẹ sự hy sinh đâu.</t>
+          <t>Tao không thể đảm bảo sẽ không có thêm tổn thất, nhưng tao sẽ ưu tiên phúc lợi của từng thành viên. Tao không coi nhẹ sự hy sinh đâu.</t>
         </is>
       </c>
     </row>
@@ -25885,7 +25885,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Giờ cậu mất cả hàng lẫn đối tác buôn bán rồi… đây là cơ hội cuối để rút lui một cách đàng hoàng đấy.</t>
+          <t>Giờ mày mất cả hàng lẫn đối tác buôn bán rồi… đây là cơ hội cuối để rút lui một cách đàng hoàng đấy.</t>
         </is>
       </c>
     </row>
@@ -27055,7 +27055,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Thật kỳ lạ, lần cuối người ta thấy Benett là ở gần &lt;color=yellow&gt;Liberty Square&lt;/color&gt;, nơi cậu gặp bác ấy.</t>
+          <t>Thật kỳ lạ, lần cuối người ta thấy Benett là ở gần &lt;color=yellow&gt;Quảng trường Tự Do&lt;/color&gt;, nơi cậu gặp bác ấy.</t>
         </is>
       </c>
     </row>
@@ -27250,7 +27250,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Nhưng khi ta nói chuyện này với hắn sau đó, hắn có vẻ chẳng biết tí gì về chi tiết cả.</t>
+          <t>Nhưng khi tao nói chuyện này với hắn sau đó, hắn có vẻ chẳng biết tí gì về chi tiết cả.</t>
         </is>
       </c>
     </row>
@@ -28162,7 +28162,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Về Hội Ánh Sáng, tôi đã giao cho "Blue Rain" và "Retriever" &lt;color=yellow&gt;pose as Capollo's agents&lt;/color&gt; và tuyên bố hợp tác vô hiệu.</t>
+          <t>Về Hội Ánh Sáng, tôi đã giao cho "Blue Rain" và "Retriever" &lt;color=yellow&gt;giả làm tay chân của Capollo&lt;/color&gt; và tuyên bố hợp tác vô hiệu.</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Mưa lại về rồi. Nhớ hồi đó ta còn nói với ông nội là ta ghét mùa mưa mà.</t>
+          <t>Mưa lại về rồi. Nhớ hồi đó tao còn nói với ông nội là tao ghét mùa mưa mà.</t>
         </is>
       </c>
     </row>
@@ -30242,7 +30242,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Dù cậu đã có một đôi Mắt Cat rồi, nhưng hãy nhận lấy viên ngọc này như một lời cảm ơn của ta. Không, viên ngọc này không phải do Forte ta tạo ra đâu. Ta chọn nó riêng cho cậu thôi.</t>
+          <t>Dù cậu đã có một đôi Mắt Mèo rồi, nhưng hãy nhận lấy viên ngọc này như một lời cảm ơn của tao. Không, viên ngọc này không phải do Forte tao tạo ra đâu. Tao chọn nó riêng cho cậu thôi.</t>
         </is>
       </c>
     </row>
@@ -31154,7 +31154,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Tôi sẽ không bao giờ quên đêm &lt;color=yellow&gt;stormy&lt;/color&gt; ấy, cũng như những thành viên đã bị cuốn vào đó.</t>
+          <t>Tôi sẽ không bao giờ quên đêm &lt;color=yellow&gt;bão tố&lt;/color&gt; ấy, cũng như những thành viên đã bị cuốn vào đó.</t>
         </is>
       </c>
     </row>
@@ -31804,7 +31804,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Ta đã cố thuyết phục hắn rời đi cùng ta, nhưng thất bại. Trong trò chơi của Ragunna, gia tộc Montelli chỉ có hai lựa chọn.</t>
+          <t>Tao đã cố thuyết phục hắn rời đi cùng tao, nhưng thất bại. Trong trò chơi của Ragunna, gia tộc Montelli chỉ có hai lựa chọn.</t>
         </is>
       </c>
     </row>
@@ -32909,7 +32909,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Nhưng sau vụ xung đột gần đây với gia đình, ta không dám chắc cậu sẽ tìm thấy họ, nói gì đến chuyện nói chuyện.</t>
+          <t>Nhưng sau vụ xung đột gần đây với gia đình, tao không dám chắc cậu sẽ tìm thấy họ, nói gì đến chuyện nói chuyện.</t>
         </is>
       </c>
     </row>
